--- a/01_Thermal/B_results/single_annular_var_params.xlsx
+++ b/01_Thermal/B_results/single_annular_var_params.xlsx
@@ -460,16 +460,16 @@
         <v>0.2</v>
       </c>
       <c r="B2" t="n">
-        <v>5.033522985421604</v>
+        <v>5.033052279130711</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3057776345550767</v>
+        <v>0.3056239944714074</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2106204920901815</v>
+        <v>0.210752420248507</v>
       </c>
       <c r="E2" t="n">
-        <v>9.999999999999979e-05</v>
+        <v>9.999999999996996e-05</v>
       </c>
     </row>
     <row r="3">
@@ -477,13 +477,13 @@
         <v>0.35</v>
       </c>
       <c r="B3" t="n">
-        <v>4.508601873877206</v>
+        <v>4.497177416740474</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3275258006741637</v>
+        <v>0.3274327497449923</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2995575376532067</v>
+        <v>0.300687128100693</v>
       </c>
       <c r="E3" t="n">
         <v>9.999999999999999e-05</v>
@@ -494,16 +494,16 @@
         <v>0.5</v>
       </c>
       <c r="B4" t="n">
-        <v>4.376975564900278</v>
+        <v>4.377473856881211</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5041205355485078</v>
+        <v>0.5039237833082832</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2564268306340854</v>
+        <v>0.2567002673970867</v>
       </c>
       <c r="E4" t="n">
-        <v>9.999999999999995e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="5">
@@ -511,13 +511,13 @@
         <v>0.75</v>
       </c>
       <c r="B5" t="n">
-        <v>2.937451566730601</v>
+        <v>2.938255286145861</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3598792348279544</v>
+        <v>0.3522596198447994</v>
       </c>
       <c r="D5" t="n">
-        <v>0.451066807036104</v>
+        <v>0.4519849543278506</v>
       </c>
       <c r="E5" t="n">
         <v>9.999999999999999e-05</v>
@@ -528,16 +528,16 @@
         <v>1.1</v>
       </c>
       <c r="B6" t="n">
-        <v>2.43791344539954</v>
+        <v>2.435955988105618</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3967853748509416</v>
+        <v>0.3963469909285288</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4208074818054103</v>
+        <v>0.4213812543802276</v>
       </c>
       <c r="E6" t="n">
-        <v>9.999999999999979e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>1.6</v>
       </c>
       <c r="B7" t="n">
-        <v>2.642972186813929</v>
+        <v>2.643112120016701</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4248063665135722</v>
+        <v>0.4247967191274478</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4268564593877036</v>
+        <v>0.4268515626110699</v>
       </c>
       <c r="E7" t="n">
-        <v>9.999999999999914e-05</v>
+        <v>9.999999999999799e-05</v>
       </c>
     </row>
     <row r="8">
@@ -562,13 +562,13 @@
         <v>2.2</v>
       </c>
       <c r="B8" t="n">
-        <v>2.082279248560511</v>
+        <v>2.082318135949508</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4056666566268314</v>
+        <v>0.4056610221435744</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5195366193603094</v>
+        <v>0.5195889724952395</v>
       </c>
       <c r="E8" t="n">
         <v>9.999999999999999e-05</v>

--- a/01_Thermal/B_results/single_annular_var_params.xlsx
+++ b/01_Thermal/B_results/single_annular_var_params.xlsx
@@ -460,16 +460,16 @@
         <v>0.2</v>
       </c>
       <c r="B2" t="n">
-        <v>5.033052279130711</v>
+        <v>4.916295944828834</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3056239944714074</v>
+        <v>0.3066769217402805</v>
       </c>
       <c r="D2" t="n">
-        <v>0.210752420248507</v>
+        <v>0.2018969531010486</v>
       </c>
       <c r="E2" t="n">
-        <v>9.999999999996996e-05</v>
+        <v>0.1193549673528184</v>
       </c>
     </row>
     <row r="3">
@@ -477,16 +477,16 @@
         <v>0.35</v>
       </c>
       <c r="B3" t="n">
-        <v>4.497177416740474</v>
+        <v>4.504554871688979</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3274327497449923</v>
+        <v>0.3280733407944455</v>
       </c>
       <c r="D3" t="n">
-        <v>0.300687128100693</v>
+        <v>0.2965147859884885</v>
       </c>
       <c r="E3" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01030739740961069</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>0.5</v>
       </c>
       <c r="B4" t="n">
-        <v>4.377473856881211</v>
+        <v>4.372379358174996</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5039237833082832</v>
+        <v>0.5034238703794722</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2567002673970867</v>
+        <v>0.2540811354115556</v>
       </c>
       <c r="E4" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.02166117169207601</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>0.75</v>
       </c>
       <c r="B5" t="n">
-        <v>2.938255286145861</v>
+        <v>3.007695963869996</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3522596198447994</v>
+        <v>0.3716909497932002</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4519849543278506</v>
+        <v>0.4232312347850639</v>
       </c>
       <c r="E5" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01755749358929044</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>1.1</v>
       </c>
       <c r="B6" t="n">
-        <v>2.435955988105618</v>
+        <v>2.439214544628072</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3963469909285288</v>
+        <v>0.3987765170195623</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4213812543802276</v>
+        <v>0.4164259091130328</v>
       </c>
       <c r="E6" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.009266379933207952</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>1.6</v>
       </c>
       <c r="B7" t="n">
-        <v>2.643112120016701</v>
+        <v>2.64378362529128</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4247967191274478</v>
+        <v>0.4252089437250119</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4268515626110699</v>
+        <v>0.4249063398721223</v>
       </c>
       <c r="E7" t="n">
-        <v>9.999999999999799e-05</v>
+        <v>0.003354883256357605</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>2.2</v>
       </c>
       <c r="B8" t="n">
-        <v>2.082318135949508</v>
+        <v>2.080269377750964</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4056610221435744</v>
+        <v>0.4072136409778495</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5195889724952395</v>
+        <v>0.514327794546161</v>
       </c>
       <c r="E8" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.006925047336243083</v>
       </c>
     </row>
   </sheetData>

--- a/01_Thermal/B_results/single_annular_var_params.xlsx
+++ b/01_Thermal/B_results/single_annular_var_params.xlsx
@@ -460,16 +460,16 @@
         <v>0.2</v>
       </c>
       <c r="B2" t="n">
-        <v>4.916295944828834</v>
+        <v>4.993168672000794</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3066769217402805</v>
+        <v>0.3064636545788689</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2018969531010486</v>
+        <v>0.2076436482913198</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1193549673528184</v>
+        <v>0.04186236843006413</v>
       </c>
     </row>
     <row r="3">
@@ -477,16 +477,16 @@
         <v>0.35</v>
       </c>
       <c r="B3" t="n">
-        <v>4.504554871688979</v>
+        <v>4.690796772703752</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3280733407944455</v>
+        <v>0.3380991221760268</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2965147859884885</v>
+        <v>0.2591356454008263</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01030739740961069</v>
+        <v>0.01243726236809802</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>0.5</v>
       </c>
       <c r="B4" t="n">
-        <v>4.372379358174996</v>
+        <v>4.348421871651814</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5034238703794722</v>
+        <v>0.5041761462783177</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2540811354115556</v>
+        <v>0.2554947066737376</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02166117169207601</v>
+        <v>0.02261286440636278</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>0.75</v>
       </c>
       <c r="B5" t="n">
-        <v>3.007695963869996</v>
+        <v>3.448422812416474</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3716909497932002</v>
+        <v>0.4346092129450429</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4232312347850639</v>
+        <v>0.3272073779322225</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01755749358929044</v>
+        <v>0.01928974500599467</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>1.1</v>
       </c>
       <c r="B6" t="n">
-        <v>2.439214544628072</v>
+        <v>2.468032511233544</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3987765170195623</v>
+        <v>0.4052700281195287</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4164259091130328</v>
+        <v>0.4130039165369583</v>
       </c>
       <c r="E6" t="n">
-        <v>0.009266379933207952</v>
+        <v>0.009247765931093733</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>1.6</v>
       </c>
       <c r="B7" t="n">
-        <v>2.64378362529128</v>
+        <v>2.664352585117351</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4252089437250119</v>
+        <v>0.4277945224493103</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4249063398721223</v>
+        <v>0.4168743271640927</v>
       </c>
       <c r="E7" t="n">
-        <v>0.003354883256357605</v>
+        <v>0.002841545163073277</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>2.2</v>
       </c>
       <c r="B8" t="n">
-        <v>2.080269377750964</v>
+        <v>2.067494124067331</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4072136409778495</v>
+        <v>0.4017020576160828</v>
       </c>
       <c r="D8" t="n">
-        <v>0.514327794546161</v>
+        <v>0.517533266127037</v>
       </c>
       <c r="E8" t="n">
-        <v>0.006925047336243083</v>
+        <v>0.006613048871428986</v>
       </c>
     </row>
   </sheetData>
